--- a/02_外部設計/04_画面遷移図.xlsx
+++ b/02_外部設計/04_画面遷移図.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\02_外部設計\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A8AC26D-F88C-415E-BFC3-56360342C3BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{086EC168-E250-482D-9F74-27A7DA10D88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="802" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="41">
   <si>
     <t>システム名称</t>
     <rPh sb="4" eb="6">
@@ -332,6 +332,28 @@
     </rPh>
     <rPh sb="3" eb="5">
       <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>一部、矢印の色が間違っていたため、要件定義書通りに修正しました。</t>
+    <rPh sb="0" eb="2">
+      <t>イチブ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヤジルシ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>マチガ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ドオ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>シュウセイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -8318,14 +8340,14 @@
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
               <a:solidFill>
-                <a:srgbClr val="FF0000"/>
+                <a:srgbClr val="0070C0"/>
               </a:solidFill>
             </a:rPr>
             <a:t>※2</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
             <a:solidFill>
-              <a:srgbClr val="FF0000"/>
+              <a:srgbClr val="0070C0"/>
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
@@ -15435,7 +15457,7 @@
       <c r="AJ47" s="39"/>
       <c r="AK47" s="39"/>
       <c r="AL47" s="38">
-        <v>45553</v>
+        <v>45576</v>
       </c>
       <c r="AM47" s="38"/>
       <c r="AN47" s="38"/>
@@ -16337,7 +16359,9 @@
       <c r="H11" s="66"/>
       <c r="I11" s="66"/>
       <c r="J11" s="66"/>
-      <c r="K11" s="66"/>
+      <c r="K11" s="66" t="s">
+        <v>27</v>
+      </c>
       <c r="L11" s="66"/>
       <c r="M11" s="66"/>
       <c r="N11" s="66"/>
@@ -16347,7 +16371,9 @@
       <c r="R11" s="66"/>
       <c r="S11" s="66"/>
       <c r="T11" s="66"/>
-      <c r="U11" s="66"/>
+      <c r="U11" s="66" t="s">
+        <v>40</v>
+      </c>
       <c r="V11" s="66"/>
       <c r="W11" s="66"/>
       <c r="X11" s="66"/>
@@ -18660,7 +18686,7 @@
       <c r="AJ1" s="99"/>
       <c r="AK1" s="99"/>
       <c r="AL1" s="101">
-        <v>45553</v>
+        <v>45576</v>
       </c>
       <c r="AM1" s="101"/>
       <c r="AN1" s="101"/>
